--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.86330042914681</v>
+        <v>1.927786319736357</v>
       </c>
       <c r="D2" t="n">
-        <v>11.50303790805834</v>
+        <v>1.869243660059481</v>
       </c>
       <c r="E2" t="n">
-        <v>41.27354183298608</v>
+        <v>6.706950547860239</v>
       </c>
       <c r="F2" t="n">
-        <v>41.17962439925137</v>
+        <v>6.691688964878348</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.09830980776723</v>
+        <v>0.5034753437621748</v>
       </c>
       <c r="D3" t="n">
-        <v>3.462669501842529</v>
+        <v>0.5626837940494109</v>
       </c>
       <c r="E3" t="n">
-        <v>41.27354183298608</v>
+        <v>6.706950547860239</v>
       </c>
       <c r="F3" t="n">
-        <v>41.17962439925137</v>
+        <v>6.691688964878348</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12.20304725773786</v>
+        <v>1.982995179382403</v>
       </c>
       <c r="D4" t="n">
-        <v>12.19789414430806</v>
+        <v>1.98215779845006</v>
       </c>
       <c r="E4" t="n">
-        <v>41.27354183298608</v>
+        <v>6.706950547860239</v>
       </c>
       <c r="F4" t="n">
-        <v>41.17962439925137</v>
+        <v>6.691688964878348</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>86.79135296899227</v>
+        <v>14.10359485746124</v>
       </c>
       <c r="D5" t="n">
-        <v>86.49430922477518</v>
+        <v>14.05532524902597</v>
       </c>
       <c r="E5" t="n">
-        <v>41.27354183298608</v>
+        <v>6.706950547860239</v>
       </c>
       <c r="F5" t="n">
-        <v>41.17962439925137</v>
+        <v>6.691688964878348</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.28019733128765</v>
+        <v>3.945532066334243</v>
       </c>
       <c r="D6" t="n">
-        <v>24.28037731249117</v>
+        <v>3.945561313279815</v>
       </c>
       <c r="E6" t="n">
-        <v>41.27354183298608</v>
+        <v>6.706950547860239</v>
       </c>
       <c r="F6" t="n">
-        <v>41.17962439925137</v>
+        <v>6.691688964878348</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.34821216942677</v>
+        <v>6.069084477531851</v>
       </c>
       <c r="D7" t="n">
-        <v>37.46131460968223</v>
+        <v>6.087463624073362</v>
       </c>
       <c r="E7" t="n">
-        <v>41.27354183298608</v>
+        <v>6.706950547860239</v>
       </c>
       <c r="F7" t="n">
-        <v>41.17962439925137</v>
+        <v>6.691688964878348</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>94.7861395335797</v>
+        <v>15.4027476742067</v>
       </c>
       <c r="D8" t="n">
-        <v>94.55538233883557</v>
+        <v>15.36524963006078</v>
       </c>
       <c r="E8" t="n">
-        <v>41.27354183298608</v>
+        <v>6.706950547860239</v>
       </c>
       <c r="F8" t="n">
-        <v>41.17962439925137</v>
+        <v>6.691688964878348</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>45.96094676578755</v>
+        <v>7.468653849440478</v>
       </c>
       <c r="D9" t="n">
-        <v>46.20260053091044</v>
+        <v>7.507922586272947</v>
       </c>
       <c r="E9" t="n">
-        <v>41.27354183298608</v>
+        <v>6.706950547860239</v>
       </c>
       <c r="F9" t="n">
-        <v>41.17962439925137</v>
+        <v>6.691688964878348</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>86.51378030373992</v>
+        <v>14.05848929935774</v>
       </c>
       <c r="D10" t="n">
-        <v>86.31052879010922</v>
+        <v>14.02546092839275</v>
       </c>
       <c r="E10" t="n">
-        <v>41.27354183298608</v>
+        <v>6.706950547860239</v>
       </c>
       <c r="F10" t="n">
-        <v>41.17962439925137</v>
+        <v>6.691688964878348</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>91.95213361162729</v>
+        <v>14.94222171188943</v>
       </c>
       <c r="D11" t="n">
-        <v>91.78113973454582</v>
+        <v>14.9144352068637</v>
       </c>
       <c r="E11" t="n">
-        <v>41.27354183298608</v>
+        <v>6.706950547860239</v>
       </c>
       <c r="F11" t="n">
-        <v>41.17962439925137</v>
+        <v>6.691688964878348</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>91.62434399200356</v>
+        <v>14.88895589870058</v>
       </c>
       <c r="D12" t="n">
-        <v>91.48394450174908</v>
+        <v>14.86614098153423</v>
       </c>
       <c r="E12" t="n">
-        <v>41.27354183298608</v>
+        <v>6.706950547860239</v>
       </c>
       <c r="F12" t="n">
-        <v>41.17962439925137</v>
+        <v>6.691688964878348</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>140.4556675026718</v>
+        <v>22.82404596918417</v>
       </c>
       <c r="D13" t="n">
-        <v>140.2888265806743</v>
+        <v>22.79693431935957</v>
       </c>
       <c r="E13" t="n">
-        <v>41.27354183298608</v>
+        <v>6.706950547860239</v>
       </c>
       <c r="F13" t="n">
-        <v>41.17962439925137</v>
+        <v>6.691688964878348</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>96.61254115224531</v>
+        <v>15.69953793723986</v>
       </c>
       <c r="D14" t="n">
-        <v>96.62279914994038</v>
+        <v>15.70120486186531</v>
       </c>
       <c r="E14" t="n">
-        <v>41.27354183298608</v>
+        <v>6.706950547860239</v>
       </c>
       <c r="F14" t="n">
-        <v>41.17962439925137</v>
+        <v>6.691688964878348</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
